--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_50_R5.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_50_R5.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.004</v>
+        <v>3.449</v>
       </c>
       <c r="E2" t="n">
-        <v>1.5932</v>
+        <v>1.9038</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4108</v>
+        <v>1.5452</v>
       </c>
       <c r="G2" t="n">
         <v>0.3521</v>
@@ -610,13 +610,13 @@
         <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2759</v>
+        <v>0.1691</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2047</v>
+        <v>0.5153</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4806</v>
+        <v>-0.3462</v>
       </c>
       <c r="V2" t="n">
         <v>1.0722</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4861</v>
+        <v>2.9797</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1907</v>
+        <v>2.6506</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2955</v>
+        <v>0.3291</v>
       </c>
       <c r="G3" t="n">
         <v>0.4555</v>
@@ -688,13 +688,13 @@
         <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1111</v>
+        <v>0.3824</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5579</v>
+        <v>-0.098</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4468</v>
+        <v>0.4804</v>
       </c>
       <c r="V3" t="n">
         <v>1.214</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. FAYE</t>
+          <t>J. MORGAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8094</v>
+        <v>0.7471</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9732</v>
+        <v>1.2435</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1638</v>
+        <v>-0.4964</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6244</v>
+        <v>1.8085</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.735</v>
+        <v>1.1694</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1105</v>
+        <v>0.6391</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.7532</v>
+        <v>2.5839</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.9741</v>
+        <v>0.9411</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2208</v>
+        <v>1.6428</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1288</v>
+        <v>-0.7754</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2391</v>
+        <v>0.2283</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1103</v>
+        <v>-1.0037</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8556</v>
+        <v>2.7834</v>
       </c>
       <c r="S4" t="n">
-        <v>3.488</v>
+        <v>-0.5612</v>
       </c>
       <c r="T4" t="n">
-        <v>3.3501</v>
+        <v>0.0514</v>
       </c>
       <c r="U4" t="n">
-        <v>0.138</v>
+        <v>-0.6126</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.7501</v>
+        <v>-1.8919</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.2862</v>
+        <v>-1.8919</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. MORGAN</t>
+          <t>J. ROBINSON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3465</v>
+        <v>0.3653</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8766</v>
+        <v>-0.0202</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.53</v>
+        <v>0.3855</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8085</v>
+        <v>-2.6344</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1694</v>
+        <v>1.5448</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6391</v>
+        <v>-4.1792</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5839</v>
+        <v>-1.9557</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9411</v>
+        <v>1.1161</v>
       </c>
       <c r="L5" t="n">
-        <v>1.6428</v>
+        <v>-3.0718</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7754</v>
+        <v>-0.6787</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2283</v>
+        <v>0.4287</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0037</v>
+        <v>-1.1074</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3917</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7834</v>
+        <v>0.6959</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0382</v>
+        <v>0.1052</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6844</v>
+        <v>-0.2631</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6462</v>
+        <v>0.3684</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.8919</v>
+        <v>3.3584</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>3.3584</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.8919</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2976</v>
+        <v>0.0391</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4603</v>
+        <v>-0.2244</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1627</v>
+        <v>0.2635</v>
       </c>
       <c r="G6" t="n">
         <v>-0.2154</v>
@@ -922,13 +922,13 @@
         <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5461</v>
+        <v>-0.2093</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2987</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2473</v>
+        <v>-0.1465</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. ROBINSON</t>
+          <t>M. FAYE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5329</v>
+        <v>-0.5484</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9519</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4191</v>
+        <v>-0.6343</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.6344</v>
+        <v>-0.6244</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5448</v>
+        <v>-0.735</v>
       </c>
       <c r="I7" t="n">
-        <v>-4.1792</v>
+        <v>0.1105</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.9557</v>
+        <v>-0.7532</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1161</v>
+        <v>-0.9741</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.0718</v>
+        <v>0.2208</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6787</v>
+        <v>0.1288</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4287</v>
+        <v>0.2391</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.1074</v>
+        <v>-0.1103</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6959</v>
+        <v>1.8556</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7929</v>
+        <v>1.1303</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1949</v>
+        <v>1.4629</v>
       </c>
       <c r="U7" t="n">
-        <v>0.402</v>
+        <v>-0.3325</v>
       </c>
       <c r="V7" t="n">
-        <v>3.3584</v>
+        <v>-1.7501</v>
       </c>
       <c r="W7" t="n">
-        <v>3.3584</v>
+        <v>0.5361</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. DOKOSSI</t>
+          <t>A. M'BAYE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1311</v>
+        <v>-1.178</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2748</v>
+        <v>-0.8958</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8563</v>
+        <v>-0.2821</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8736</v>
+        <v>-1.5318</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8907</v>
+        <v>-2.1307</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.0171</v>
+        <v>0.5989</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6669</v>
+        <v>-0.7457</v>
       </c>
       <c r="K8" t="n">
-        <v>1.6301</v>
+        <v>-2.191</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0368</v>
+        <v>1.4453</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7933</v>
+        <v>-0.7861</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2606</v>
+        <v>0.0602</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0539</v>
+        <v>-0.8464</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.3195</v>
+        <v>-1.3917</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6959</v>
+        <v>2.3195</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8329</v>
+        <v>-0.5739</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3778</v>
+        <v>0.1693</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4551</v>
+        <v>-0.7433</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3903</v>
+        <v>-1.4239</v>
       </c>
       <c r="E9" t="n">
         <v>-1.5832</v>
       </c>
       <c r="F9" t="n">
-        <v>0.193</v>
+        <v>0.1593</v>
       </c>
       <c r="G9" t="n">
         <v>-0.0429</v>
@@ -1156,13 +1156,13 @@
         <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4195</v>
+        <v>-0.4531</v>
       </c>
       <c r="T9" t="n">
         <v>-0.2987</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1208</v>
+        <v>-0.1544</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Y. OUATTARA</t>
+          <t>A. DOKOSSI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.218</v>
+        <v>-1.5236</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8159</v>
+        <v>-0.8018</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5979</v>
+        <v>-0.7219</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.2089</v>
+        <v>0.8736</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.2558</v>
+        <v>1.8907</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0469</v>
+        <v>-1.0171</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.1912</v>
+        <v>1.6669</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.3484</v>
+        <v>1.6301</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1571</v>
+        <v>0.0368</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0177</v>
+        <v>-0.7933</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0926</v>
+        <v>0.2606</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1103</v>
+        <v>-1.0539</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6959</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R10" t="n">
         <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2951</v>
+        <v>0.4404</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3031</v>
+        <v>-0.1491</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9919</v>
+        <v>0.5895</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2584</v>
+        <v>-1.7649</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1884</v>
+        <v>-2.7285</v>
       </c>
       <c r="F11" t="n">
-        <v>0.93</v>
+        <v>0.9636</v>
       </c>
       <c r="G11" t="n">
         <v>-3.0004</v>
@@ -1312,13 +1312,13 @@
         <v>0.4639</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2781</v>
+        <v>0.7716</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.326</v>
+        <v>0.134</v>
       </c>
       <c r="U11" t="n">
-        <v>0.604</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. M'BAYE</t>
+          <t>Y. OUATTARA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.4816</v>
+        <v>-2.4987</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7962</v>
+        <v>-2.8278</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6854</v>
+        <v>0.329</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.5318</v>
+        <v>-4.2089</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.1307</v>
+        <v>-4.2558</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5989</v>
+        <v>0.0469</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7457</v>
+        <v>-4.1912</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.191</v>
+        <v>-4.3484</v>
       </c>
       <c r="L12" t="n">
-        <v>1.4453</v>
+        <v>0.1571</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7861</v>
+        <v>-0.0177</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0602</v>
+        <v>0.0926</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8464</v>
+        <v>-0.1103</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.3195</v>
+        <v>0.6959</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.8776</v>
+        <v>1.0143</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.731</v>
+        <v>0.2912</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.1466</v>
+        <v>0.7231</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.5061</v>
+        <v>-3.3191</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.0082</v>
+        <v>-2.754</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4979</v>
+        <v>-0.5651</v>
       </c>
       <c r="G13" t="n">
         <v>-2.2006</v>
@@ -1468,13 +1468,13 @@
         <v>2.7834</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3776</v>
+        <v>-0.1907</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8804</v>
+        <v>0.3738</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4973</v>
+        <v>-0.5645</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.169999999999998</v>
+        <v>-4.6764</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.445200000000001</v>
+        <v>-5.9518</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2756</v>
+        <v>1.2754</v>
       </c>
       <c r="G14" t="n">
         <v>-10.9691</v>
@@ -1522,10 +1522,10 @@
         <v>-7.004</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.639999999999999</v>
+        <v>-3.64</v>
       </c>
       <c r="L14" t="n">
-        <v>-3.364100000000001</v>
+        <v>-3.3641</v>
       </c>
       <c r="M14" t="n">
         <v>-3.9653</v>
@@ -1534,7 +1534,7 @@
         <v>2.3907</v>
       </c>
       <c r="O14" t="n">
-        <v>-6.356099999999999</v>
+        <v>-6.3561</v>
       </c>
       <c r="P14" t="n">
         <v>3.4793</v>
@@ -1546,13 +1546,13 @@
         <v>16.2367</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5315999999999996</v>
+        <v>2.0251</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6324999999999993</v>
+        <v>2.1262</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1010000000000001</v>
+        <v>-0.1010000000000002</v>
       </c>
       <c r="V14" t="n">
         <v>0.7886000000000002</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.5354</v>
+        <v>4.7719</v>
       </c>
       <c r="E15" t="n">
-        <v>6.8915</v>
+        <v>5.0042</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.356</v>
+        <v>-0.2324</v>
       </c>
       <c r="G15" t="n">
         <v>2.753</v>
@@ -1624,13 +1624,13 @@
         <v>2.0876</v>
       </c>
       <c r="S15" t="n">
-        <v>3.3391</v>
+        <v>1.5755</v>
       </c>
       <c r="T15" t="n">
-        <v>3.0593</v>
+        <v>1.172</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2798</v>
+        <v>0.4035</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2525</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. GINAT</t>
+          <t>A. BLAKENEY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9644</v>
+        <v>2.2875</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.5326</v>
+        <v>0.6896</v>
       </c>
       <c r="F16" t="n">
-        <v>3.497</v>
+        <v>1.5979</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3613</v>
+        <v>0.7524</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2978</v>
+        <v>-1.2953</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0636</v>
+        <v>2.0476</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3069</v>
+        <v>0.3091</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5546</v>
+        <v>-2.0061</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.2477</v>
+        <v>2.3152</v>
       </c>
       <c r="M16" t="n">
-        <v>1.0545</v>
+        <v>0.4433</v>
       </c>
       <c r="N16" t="n">
-        <v>0.7432</v>
+        <v>0.7109</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3113</v>
+        <v>-0.2676</v>
       </c>
       <c r="P16" t="n">
+        <v>1.1598</v>
+      </c>
+      <c r="Q16" t="n">
         <v>-0.232</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-1.3917</v>
-      </c>
       <c r="R16" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6932</v>
+        <v>0.3754</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5895</v>
+        <v>-0.4597</v>
       </c>
       <c r="U16" t="n">
-        <v>1.2828</v>
+        <v>0.8351</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8991</v>
+        <v>2.2637</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1304</v>
+        <v>-0.2484</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0295</v>
+        <v>2.5121</v>
       </c>
       <c r="G17" t="n">
         <v>3.8004</v>
@@ -1780,13 +1780,13 @@
         <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.293</v>
+        <v>0.0716</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0553</v>
+        <v>-0.0626</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3484</v>
+        <v>0.1342</v>
       </c>
       <c r="V17" t="n">
         <v>-1.6083</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. BLAKENEY</t>
+          <t>J. MOTLEY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.8665</v>
+        <v>2.1996</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3357</v>
+        <v>0.1861</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5307</v>
+        <v>2.0134</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7524</v>
+        <v>3.544</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.2953</v>
+        <v>0.5894</v>
       </c>
       <c r="I18" t="n">
-        <v>2.0476</v>
+        <v>2.9546</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3091</v>
+        <v>1.5786</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.0061</v>
+        <v>0.5615</v>
       </c>
       <c r="L18" t="n">
-        <v>2.3152</v>
+        <v>1.0171</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4433</v>
+        <v>1.9654</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7109</v>
+        <v>0.0279</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2676</v>
+        <v>1.9375</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1598</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.232</v>
+        <v>-2.5515</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0457</v>
+        <v>0.1169</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8136</v>
+        <v>0.0868</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7679</v>
+        <v>0.0301</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
       <c r="W18" t="n">
         <v>1.0722</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0722</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MOTLEY</t>
+          <t>T. GINAT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.7678</v>
+        <v>1.4774</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3041</v>
+        <v>-1.4147</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4637</v>
+        <v>2.8921</v>
       </c>
       <c r="G19" t="n">
-        <v>3.544</v>
+        <v>1.3613</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5894</v>
+        <v>1.2978</v>
       </c>
       <c r="I19" t="n">
-        <v>2.9546</v>
+        <v>0.0636</v>
       </c>
       <c r="J19" t="n">
-        <v>1.5786</v>
+        <v>0.3069</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5615</v>
+        <v>0.5546</v>
       </c>
       <c r="L19" t="n">
-        <v>1.0171</v>
+        <v>-0.2477</v>
       </c>
       <c r="M19" t="n">
-        <v>1.9654</v>
+        <v>1.0545</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0279</v>
+        <v>0.7432</v>
       </c>
       <c r="O19" t="n">
-        <v>1.9375</v>
+        <v>0.3113</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.8556</v>
+        <v>-0.232</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.5515</v>
+        <v>-1.3917</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.315</v>
+        <v>0.2063</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2047</v>
+        <v>-0.4716</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5197000000000001</v>
+        <v>0.6778</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3943</v>
+        <v>0.1418</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. BRYANT</t>
+          <t>V. MICIC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4939</v>
+        <v>0.2666</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0623</v>
+        <v>0.4554</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5684</v>
+        <v>-0.1888</v>
       </c>
       <c r="G21" t="n">
-        <v>1.7242</v>
+        <v>1.0619</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.4513</v>
+        <v>0.0482</v>
       </c>
       <c r="I21" t="n">
-        <v>3.1754</v>
+        <v>1.0137</v>
       </c>
       <c r="J21" t="n">
-        <v>0.924</v>
+        <v>0.7443</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.4684</v>
+        <v>0.3564</v>
       </c>
       <c r="L21" t="n">
-        <v>2.3923</v>
+        <v>0.3879</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8002</v>
+        <v>0.3176</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0171</v>
+        <v>-0.3082</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7831</v>
+        <v>0.6258</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.6237</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q21" t="n">
         <v>-2.5515</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5944</v>
+        <v>-0.4758</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.507</v>
+        <v>0.1182</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.5939</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0722</v>
+        <v>2.1444</v>
       </c>
       <c r="X21" t="n">
         <v>-1.0722</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>V. MICIC</t>
+          <t>E. BRYANT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.89</v>
+        <v>0.0915</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2523</v>
+        <v>-0.3546</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6377</v>
+        <v>0.446</v>
       </c>
       <c r="G22" t="n">
-        <v>1.0619</v>
+        <v>1.7242</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0482</v>
+        <v>-1.4513</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0137</v>
+        <v>3.1754</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7443</v>
+        <v>0.924</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3564</v>
+        <v>-1.4684</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3879</v>
+        <v>2.3923</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3176</v>
+        <v>0.8002</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3082</v>
+        <v>0.0171</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6258</v>
+        <v>0.7831</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.3917</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q22" t="n">
         <v>-2.5515</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6324</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5895</v>
+        <v>0.2008</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0429</v>
+        <v>-0.2098</v>
       </c>
       <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
         <v>1.0722</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.1444</v>
       </c>
       <c r="X22" t="n">
         <v>-1.0722</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7102</v>
+        <v>-0.8288</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2137</v>
+        <v>-0.6239</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4965</v>
+        <v>-0.2048</v>
       </c>
       <c r="G23" t="n">
         <v>0.3652</v>
@@ -2248,13 +2248,13 @@
         <v>1.1598</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.0058</v>
+        <v>-1.1244</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8883</v>
+        <v>-0.2985</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1176</v>
+        <v>-0.8259</v>
       </c>
       <c r="V23" t="n">
         <v>0.3943</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.1487</v>
+        <v>-2.4189</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.0064</v>
+        <v>-2.4783</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1423</v>
+        <v>0.0594</v>
       </c>
       <c r="G24" t="n">
         <v>-3.709</v>
@@ -2326,13 +2326,13 @@
         <v>1.3917</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7046</v>
+        <v>0.4345</v>
       </c>
       <c r="T24" t="n">
-        <v>0.8338</v>
+        <v>0.362</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1291</v>
+        <v>0.0725</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5361</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.9349</v>
+        <v>-2.6826</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.6039</v>
+        <v>-1.4859</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.3311</v>
+        <v>-1.1967</v>
       </c>
       <c r="G25" t="n">
         <v>-0.9987</v>
@@ -2404,13 +2404,13 @@
         <v>0.9278</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1502</v>
+        <v>0.1021</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5895</v>
+        <v>-0.4716</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4393</v>
+        <v>0.5737</v>
       </c>
       <c r="V25" t="n">
         <v>-0.3943</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>6.169999999999999</v>
+        <v>7.742400000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.3449999999999995</v>
+        <v>-0.3452000000000011</v>
       </c>
       <c r="F26" t="n">
-        <v>6.5149</v>
+        <v>8.087400000000001</v>
       </c>
       <c r="G26" t="n">
         <v>10.9692</v>
@@ -2455,13 +2455,13 @@
         <v>9.7201</v>
       </c>
       <c r="J26" t="n">
-        <v>3.965400000000001</v>
+        <v>3.965399999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.390700000000001</v>
+        <v>-2.3907</v>
       </c>
       <c r="L26" t="n">
-        <v>6.356099999999999</v>
+        <v>6.356100000000001</v>
       </c>
       <c r="M26" t="n">
         <v>7.004</v>
@@ -2482,16 +2482,16 @@
         <v>12.7576</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.5315999999999999</v>
+        <v>1.0411</v>
       </c>
       <c r="T26" t="n">
-        <v>0.1009999999999998</v>
+        <v>0.1010999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.6325999999999998</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.7886000000000002</v>
+        <v>-0.7886</v>
       </c>
       <c r="W26" t="n">
         <v>11.8253</v>
